--- a/00_Tracker/Think_Like_a_Scientist_Tracker.xlsx
+++ b/00_Tracker/Think_Like_a_Scientist_Tracker.xlsx
@@ -832,7 +832,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="8.5" customWidth="1" min="9" max="9"/>
     <col width="8.5" customWidth="1" min="10" max="10"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Language support</t>
+          <t>Language band (1, 2 or 3)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
@@ -2699,7 +2699,7 @@
       <formula>AJ2="Check"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="I2:I25 S2:S25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Skills check" error="Enter a whole number from 0 to 20. Leave blank if absent." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
@@ -2718,8 +2718,11 @@
     <dataValidation sqref="E2:E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose a role from the list." type="list">
       <formula1>Lists!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G25 AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
+    <dataValidation sqref="AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
       <formula1>Lists!$C$2:$C$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Language band" error="Enter 1, 2 or 3 (see Teacher Guide Section 4) or leave blank." type="list">
+      <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2741,7 +2744,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="8.5" customWidth="1" min="9" max="9"/>
     <col width="8.5" customWidth="1" min="10" max="10"/>
@@ -2809,7 +2812,7 @@
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Language support</t>
+          <t>Language band (1, 2 or 3)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
@@ -4608,7 +4611,7 @@
       <formula>AJ2="Check"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="I2:I25 S2:S25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Skills check" error="Enter a whole number from 0 to 20. Leave blank if absent." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
@@ -4627,8 +4630,11 @@
     <dataValidation sqref="E2:E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose a role from the list." type="list">
       <formula1>Lists!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G25 AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
+    <dataValidation sqref="AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
       <formula1>Lists!$C$2:$C$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Language band" error="Enter 1, 2 or 3 (see Teacher Guide Section 4) or leave blank." type="list">
+      <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4650,7 +4656,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="8.5" customWidth="1" min="9" max="9"/>
     <col width="8.5" customWidth="1" min="10" max="10"/>
@@ -4718,7 +4724,7 @@
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Language support</t>
+          <t>Language band (1, 2 or 3)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
@@ -6517,7 +6523,7 @@
       <formula>AJ2="Check"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="I2:I25 S2:S25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Skills check" error="Enter a whole number from 0 to 20. Leave blank if absent." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
@@ -6536,8 +6542,11 @@
     <dataValidation sqref="E2:E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose a role from the list." type="list">
       <formula1>Lists!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G25 AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
+    <dataValidation sqref="AL2:AL25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type Y or leave blank." type="list">
       <formula1>Lists!$C$2:$C$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Language band" error="Enter 1, 2 or 3 (see Teacher Guide Section 4) or leave blank." type="list">
+      <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10550,7 +10559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10569,6 +10578,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -10586,6 +10600,9 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -10598,6 +10615,9 @@
           <t>Measurer</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -10609,6 +10629,9 @@
         <is>
           <t>Recorder</t>
         </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
